--- a/_plugins/echarts-v6.0.0/timeline.xlsx
+++ b/_plugins/echarts-v6.0.0/timeline.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17925"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>日期</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>发布小小星空v2.0.0</t>
+  </si>
+  <si>
+    <t>发布小小星空v2.0.11</t>
   </si>
 </sst>
 </file>
@@ -153,7 +156,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,13 +168,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -636,130 +632,130 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -773,10 +769,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1098,7 +1094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.125" customWidth="1"/>
@@ -2093,6 +2089,17 @@
         <v>37</v>
       </c>
     </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="2">
+        <v>46128</v>
+      </c>
+      <c r="B111">
+        <v>121537</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G1" r:id="rId1" display="https://echarts.apache.org/zh/spreadsheet.html"/>

--- a/_plugins/echarts-v6.0.0/timeline.xlsx
+++ b/_plugins/echarts-v6.0.0/timeline.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>日期</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>发布小小星空v2.0.11</t>
+  </si>
+  <si>
+    <t>发布小小星空v2.1.0</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.125" customWidth="1"/>
@@ -1115,7 +1118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:7">
       <c r="A2" s="2">
         <v>42972</v>
       </c>
@@ -1126,7 +1129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>42987</v>
       </c>
@@ -1137,7 +1140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>42990</v>
       </c>
@@ -1148,7 +1151,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:7">
       <c r="A5" s="2">
         <v>42992</v>
       </c>
@@ -1159,7 +1162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:7">
       <c r="A6" s="2">
         <v>43000</v>
       </c>
@@ -1167,7 +1170,7 @@
         <v>103083</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:7">
       <c r="A7" s="2">
         <v>43001</v>
       </c>
@@ -1175,7 +1178,7 @@
         <v>103124</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:7">
       <c r="A8" s="2">
         <v>43002</v>
       </c>
@@ -1183,7 +1186,7 @@
         <v>103133</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:7">
       <c r="A9" s="2">
         <v>43003</v>
       </c>
@@ -1191,7 +1194,7 @@
         <v>103174</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:7">
       <c r="A10" s="2">
         <v>43004</v>
       </c>
@@ -1199,7 +1202,7 @@
         <v>103172</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:7">
       <c r="A11" s="2">
         <v>43005</v>
       </c>
@@ -1207,7 +1210,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:7">
       <c r="A12" s="2">
         <v>43006</v>
       </c>
@@ -1215,7 +1218,7 @@
         <v>103194</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:7">
       <c r="A13" s="2">
         <v>43008</v>
       </c>
@@ -1223,7 +1226,7 @@
         <v>103199</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:7">
       <c r="A14" s="2">
         <v>43009</v>
       </c>
@@ -1231,7 +1234,7 @@
         <v>103214</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:7">
       <c r="A15" s="2">
         <v>43015</v>
       </c>
@@ -1242,7 +1245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:7">
       <c r="A16" s="2">
         <v>43020</v>
       </c>
@@ -1286,7 +1289,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:3">
       <c r="A20" s="2">
         <v>43026</v>
       </c>
@@ -1294,7 +1297,7 @@
         <v>103733</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:3">
       <c r="A21" s="2">
         <v>43030</v>
       </c>
@@ -1302,7 +1305,7 @@
         <v>103933</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:3">
       <c r="A22" s="2">
         <v>43032</v>
       </c>
@@ -1310,7 +1313,7 @@
         <v>103997</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:3">
       <c r="A23" s="2">
         <v>43033</v>
       </c>
@@ -1318,7 +1321,7 @@
         <v>104042</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:3">
       <c r="A24" s="2">
         <v>43034</v>
       </c>
@@ -1326,7 +1329,7 @@
         <v>104076</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:3">
       <c r="A25" s="2">
         <v>43035</v>
       </c>
@@ -1334,7 +1337,7 @@
         <v>104110</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:3">
       <c r="A26" s="2">
         <v>43036</v>
       </c>
@@ -1342,7 +1345,7 @@
         <v>104133</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:3">
       <c r="A27" s="2">
         <v>43038</v>
       </c>
@@ -1350,7 +1353,7 @@
         <v>104276</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:3">
       <c r="A28" s="2">
         <v>43039</v>
       </c>
@@ -1358,7 +1361,7 @@
         <v>104356</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:3">
       <c r="A29" s="2">
         <v>43040</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>104482</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:3">
       <c r="A30" s="2">
         <v>43042</v>
       </c>
@@ -1374,7 +1377,7 @@
         <v>104698</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:3">
       <c r="A31" s="2">
         <v>43044</v>
       </c>
@@ -1382,7 +1385,7 @@
         <v>104791</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:3">
       <c r="A32" s="2">
         <v>43045</v>
       </c>
@@ -1390,7 +1393,7 @@
         <v>104873</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:3">
       <c r="A33" s="2">
         <v>43046</v>
       </c>
@@ -1398,7 +1401,7 @@
         <v>104963</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:3">
       <c r="A34" s="2">
         <v>43047</v>
       </c>
@@ -1406,7 +1409,7 @@
         <v>105094</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:3">
       <c r="A35" s="2">
         <v>43048</v>
       </c>
@@ -1414,7 +1417,7 @@
         <v>105122</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:3">
       <c r="A36" s="2">
         <v>43050</v>
       </c>
@@ -1422,7 +1425,7 @@
         <v>105423</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:3">
       <c r="A37" s="2">
         <v>43053</v>
       </c>
@@ -1430,7 +1433,7 @@
         <v>105539</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:3">
       <c r="A38" s="2">
         <v>43056</v>
       </c>
@@ -1460,7 +1463,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:3">
       <c r="A41" s="2">
         <v>43065</v>
       </c>
@@ -1468,7 +1471,7 @@
         <v>105448</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:3">
       <c r="A42" s="2">
         <v>43067</v>
       </c>
@@ -1476,7 +1479,7 @@
         <v>105539</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:3">
       <c r="A43" s="2">
         <v>43068</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>105600</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:3">
       <c r="A44" s="2">
         <v>43069</v>
       </c>
@@ -1492,7 +1495,7 @@
         <v>105620</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:3">
       <c r="A45" s="2">
         <v>43073</v>
       </c>
@@ -1500,7 +1503,7 @@
         <v>105741</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:3">
       <c r="A46" s="2">
         <v>43074</v>
       </c>
@@ -1541,7 +1544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:3">
       <c r="A50" s="2">
         <v>43095</v>
       </c>
@@ -1549,7 +1552,7 @@
         <v>106273</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:3">
       <c r="A51" s="2">
         <v>43097</v>
       </c>
@@ -1557,7 +1560,7 @@
         <v>106309</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:3">
       <c r="A52" s="2">
         <v>43108</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>106333</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:3">
       <c r="A53" s="2">
         <v>43112</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:3">
       <c r="A56" s="2">
         <v>43120</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>106427</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:3">
       <c r="A57" s="2">
         <v>43122</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:3">
       <c r="A59" s="2">
         <v>43125</v>
       </c>
@@ -1630,7 +1633,7 @@
         <v>106467</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:3">
       <c r="A60" s="2">
         <v>43132</v>
       </c>
@@ -1638,7 +1641,7 @@
         <v>106496</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:3">
       <c r="A61" s="2">
         <v>43138</v>
       </c>
@@ -1646,7 +1649,7 @@
         <v>106528</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:3">
       <c r="A62" s="2">
         <v>43144</v>
       </c>
@@ -1654,7 +1657,7 @@
         <v>106577</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:3">
       <c r="A63" s="2">
         <v>43155</v>
       </c>
@@ -1662,7 +1665,7 @@
         <v>106616</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:3">
       <c r="A64" s="2">
         <v>43168</v>
       </c>
@@ -1670,7 +1673,7 @@
         <v>124825</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:3">
       <c r="A65" s="2">
         <v>43179</v>
       </c>
@@ -1700,7 +1703,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:3">
       <c r="A68" s="2">
         <v>43219</v>
       </c>
@@ -1708,7 +1711,7 @@
         <v>107142</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:3">
       <c r="A69" s="2">
         <v>43224</v>
       </c>
@@ -1727,7 +1730,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:3">
       <c r="A71" s="2">
         <v>43248</v>
       </c>
@@ -1735,7 +1738,7 @@
         <v>106149</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:3">
       <c r="A72" s="2">
         <v>43254</v>
       </c>
@@ -1743,7 +1746,7 @@
         <v>106280</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:3">
       <c r="A73" s="2">
         <v>43261</v>
       </c>
@@ -1751,7 +1754,7 @@
         <v>106637</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:3">
       <c r="A74" s="2">
         <v>43268</v>
       </c>
@@ -1781,7 +1784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:3">
       <c r="A77" s="2">
         <v>43320</v>
       </c>
@@ -1800,7 +1803,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:3">
       <c r="A79" s="2">
         <v>43332</v>
       </c>
@@ -1808,7 +1811,7 @@
         <v>110296</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:3">
       <c r="A80" s="2">
         <v>43338</v>
       </c>
@@ -1816,7 +1819,7 @@
         <v>110538</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:3">
       <c r="A81" s="2">
         <v>43347</v>
       </c>
@@ -1824,7 +1827,7 @@
         <v>110680</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:3">
       <c r="A82" s="2">
         <v>43352</v>
       </c>
@@ -1832,7 +1835,7 @@
         <v>110775</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:3">
       <c r="A83" s="2">
         <v>43400</v>
       </c>
@@ -1840,7 +1843,7 @@
         <v>111536</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:3">
       <c r="A84" s="2">
         <v>43409</v>
       </c>
@@ -1848,7 +1851,7 @@
         <v>111893</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:3">
       <c r="A85" s="2">
         <v>43423</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>112102</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:3">
       <c r="A86" s="2">
         <v>43430</v>
       </c>
@@ -1864,7 +1867,7 @@
         <v>112253</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:3">
       <c r="A87" s="2">
         <v>43437</v>
       </c>
@@ -1872,7 +1875,7 @@
         <v>112377</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:3">
       <c r="A88" s="2">
         <v>43443</v>
       </c>
@@ -1880,7 +1883,7 @@
         <v>112498</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:3">
       <c r="A89" s="2">
         <v>43451</v>
       </c>
@@ -1888,7 +1891,7 @@
         <v>112544</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:3">
       <c r="A90" s="2">
         <v>43474</v>
       </c>
@@ -1896,7 +1899,7 @@
         <v>112729</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:3">
       <c r="A91" s="2">
         <v>43518</v>
       </c>
@@ -1904,7 +1907,7 @@
         <v>112877</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:3">
       <c r="A92" s="2">
         <v>43535</v>
       </c>
@@ -1923,7 +1926,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:3">
       <c r="A94" s="2">
         <v>43590</v>
       </c>
@@ -1931,7 +1934,7 @@
         <v>113629</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:3">
       <c r="A95" s="2">
         <v>43906</v>
       </c>
@@ -1972,7 +1975,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:3">
       <c r="A99" s="2">
         <v>44014</v>
       </c>
@@ -1991,7 +1994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:3">
       <c r="A101" s="2">
         <v>44051</v>
       </c>
@@ -2010,7 +2013,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:3">
       <c r="A103" s="2">
         <v>44083</v>
       </c>
@@ -2018,7 +2021,7 @@
         <v>120334</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:3">
       <c r="A104" s="2">
         <v>44093</v>
       </c>
@@ -2037,7 +2040,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:3">
       <c r="A106" s="2">
         <v>44321</v>
       </c>
@@ -2098,6 +2101,17 @@
       </c>
       <c r="C111" s="3" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B112">
+        <v>121647</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
